--- a/public/downloads/ShiLong-term2021.xlsx
+++ b/public/downloads/ShiLong-term2021.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>HO</t>
@@ -659,10 +682,10 @@
         <v>78</v>
       </c>
       <c r="N3" s="5">
-        <v>617.2888915538788</v>
+        <v>617288.8915538788</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03188805101528457</v>
+        <v>31.88805101528457</v>
       </c>
       <c r="P3" s="5">
         <v>19358</v>
@@ -709,10 +732,10 @@
         <v>78</v>
       </c>
       <c r="N4" s="5">
-        <v>997.7070710659027</v>
+        <v>997707.0710659027</v>
       </c>
       <c r="O4" s="4">
-        <v>0.06235279489193817</v>
+        <v>62.35279489193817</v>
       </c>
       <c r="P4" s="5">
         <v>16001</v>
@@ -759,10 +782,10 @@
         <v>78</v>
       </c>
       <c r="N5" s="5">
-        <v>2357.904868841171</v>
+        <v>2357904.868841171</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1451822467114815</v>
+        <v>145.1822467114815</v>
       </c>
       <c r="P5" s="5">
         <v>16241</v>
@@ -809,10 +832,10 @@
         <v>78</v>
       </c>
       <c r="N6" s="5">
-        <v>1442.456951379776</v>
+        <v>1442456.951379776</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08400541327702382</v>
+        <v>84.00541327702382</v>
       </c>
       <c r="P6" s="5">
         <v>17171</v>
@@ -859,10 +882,10 @@
         <v>78</v>
       </c>
       <c r="N7" s="5">
-        <v>3639.257705688477</v>
+        <v>3639257.705688477</v>
       </c>
       <c r="O7" s="4">
-        <v>0.2758476241710359</v>
+        <v>275.8476241710359</v>
       </c>
       <c r="P7" s="5">
         <v>13193</v>
@@ -909,10 +932,10 @@
         <v>78</v>
       </c>
       <c r="N8" s="5">
-        <v>318.0313701629639</v>
+        <v>318031.3701629639</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01726929681597328</v>
+        <v>17.26929681597328</v>
       </c>
       <c r="P8" s="5">
         <v>18416</v>
@@ -959,10 +982,10 @@
         <v>78</v>
       </c>
       <c r="N9" s="5">
-        <v>568.0487802028656</v>
+        <v>568048.7802028656</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03111402641194422</v>
+        <v>31.11402641194422</v>
       </c>
       <c r="P9" s="5">
         <v>18257</v>
@@ -1009,10 +1032,10 @@
         <v>78</v>
       </c>
       <c r="N10" s="5">
-        <v>1544.588921546936</v>
+        <v>1544588.921546936</v>
       </c>
       <c r="O10" s="4">
-        <v>0.105670720499893</v>
+        <v>105.670720499893</v>
       </c>
       <c r="P10" s="5">
         <v>14617</v>
@@ -1059,10 +1082,10 @@
         <v>78</v>
       </c>
       <c r="N11" s="5">
-        <v>730.8494210243225</v>
+        <v>730849.4210243225</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04177237202928227</v>
+        <v>41.77237202928227</v>
       </c>
       <c r="P11" s="5">
         <v>17496</v>
@@ -1109,10 +1132,10 @@
         <v>78</v>
       </c>
       <c r="N12" s="5">
-        <v>398.6188523769379</v>
+        <v>398618.8523769379</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02299105158478128</v>
+        <v>22.99105158478128</v>
       </c>
       <c r="P12" s="5">
         <v>17338</v>
@@ -1159,10 +1182,10 @@
         <v>78</v>
       </c>
       <c r="N13" s="5">
-        <v>1307.735147953033</v>
+        <v>1307735.147953033</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07570540395698931</v>
+        <v>75.70540395698931</v>
       </c>
       <c r="P13" s="5">
         <v>17274</v>
@@ -1209,10 +1232,10 @@
         <v>78</v>
       </c>
       <c r="N14" s="5">
-        <v>8082.852641820908</v>
+        <v>8082852.641820908</v>
       </c>
       <c r="O14" s="4">
-        <v>0.3859821709479446</v>
+        <v>385.9821709479446</v>
       </c>
       <c r="P14" s="5">
         <v>20941</v>
@@ -1259,10 +1282,10 @@
         <v>78</v>
       </c>
       <c r="N15" s="5">
-        <v>5334.886476993561</v>
+        <v>5334886.476993561</v>
       </c>
       <c r="O15" s="4">
-        <v>0.3870066359806718</v>
+        <v>387.0066359806718</v>
       </c>
       <c r="P15" s="5">
         <v>13785</v>
@@ -1309,10 +1332,10 @@
         <v>78</v>
       </c>
       <c r="N16" s="5">
-        <v>2035.70921254158</v>
+        <v>2035709.21254158</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1011985092732939</v>
+        <v>101.1985092732939</v>
       </c>
       <c r="P16" s="5">
         <v>20116</v>
@@ -1359,10 +1382,10 @@
         <v>78</v>
       </c>
       <c r="N17" s="5">
-        <v>1380.213397741318</v>
+        <v>1380213.397741318</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1025037800030685</v>
+        <v>102.5037800030685</v>
       </c>
       <c r="P17" s="5">
         <v>13465</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,132 +1497,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4420283323552955</v>
+        <v>0.3583712080443892</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4589025161898962</v>
+        <v>0.3904232196406178</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3776992357168852</v>
+        <v>0.2895297071355322</v>
       </c>
       <c r="E3" s="4">
-        <v>80.94583987441131</v>
+        <v>80.03924646781792</v>
       </c>
       <c r="F3" s="4">
-        <v>83.041645155738</v>
+        <v>80.37299948373717</v>
       </c>
       <c r="G3" s="5">
         <v>26</v>
       </c>
       <c r="H3" s="5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3133568264969859</v>
+      </c>
+      <c r="O3" s="5">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3670391123904735</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4087520575500589</v>
+      </c>
+      <c r="R3" s="5">
+        <v>21</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2808989160060182</v>
+        <v>0.3019225004519022</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2713124555258553</v>
+        <v>0.1277013582434586</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2541313005330438</v>
+        <v>0.2707822085099846</v>
       </c>
       <c r="E4" s="4">
-        <v>80.09157509157504</v>
+        <v>73.06384092098375</v>
       </c>
       <c r="F4" s="4">
-        <v>83.06874892445096</v>
+        <v>55.01290655653083</v>
       </c>
       <c r="G4" s="5">
         <v>26</v>
       </c>
       <c r="H4" s="5">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.02304068856405931</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3140389522172002</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1233324178772955</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3140860059165246</v>
+        <v>0.4996627554989069</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3464119540212494</v>
+        <v>0.2724021460357266</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2860096262920347</v>
+        <v>0.3250057131415533</v>
       </c>
       <c r="E5" s="4">
-        <v>80.64756671899534</v>
+        <v>78.51648351648348</v>
       </c>
       <c r="F5" s="4">
-        <v>84.93675787299939</v>
+        <v>79.06943727413505</v>
       </c>
       <c r="G5" s="5">
         <v>26</v>
       </c>
       <c r="H5" s="5">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.2347413421850638</v>
+      </c>
+      <c r="O5" s="5">
+        <v>15</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.469236806382682</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4219404366680202</v>
+      </c>
+      <c r="R5" s="5">
+        <v>15</v>
+      </c>
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,119 +1797,173 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.36348272752706</v>
+        <v>0.5344161811945386</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3334768133515809</v>
+        <v>0.4953863156943257</v>
       </c>
       <c r="D3" s="4">
-        <v>0.294321959698797</v>
+        <v>0.4649490767962513</v>
       </c>
       <c r="E3" s="4">
-        <v>79.90973312401886</v>
+        <v>76.72161172161171</v>
       </c>
       <c r="F3" s="4">
-        <v>81.20375150576427</v>
+        <v>76.82369643779039</v>
       </c>
       <c r="G3" s="5">
         <v>26</v>
       </c>
       <c r="H3" s="5">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I3" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.3149463918230921</v>
+      </c>
+      <c r="O3" s="5">
+        <v>16</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.394290313813107</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2525716384057608</v>
+      </c>
+      <c r="R3" s="5">
+        <v>16</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3328713566121166</v>
+        <v>0.5497790542897139</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1442794631009039</v>
+        <v>0.6241584252035276</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2189784997167036</v>
+        <v>0.5650815778010099</v>
       </c>
       <c r="E4" s="4">
-        <v>73.66954474097336</v>
+        <v>73.10832025117739</v>
       </c>
       <c r="F4" s="4">
-        <v>58.69428669764188</v>
+        <v>63.9825331268292</v>
       </c>
       <c r="G4" s="5">
         <v>26</v>
       </c>
       <c r="H4" s="5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I4" s="5">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J4" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.6146466796270431</v>
+      </c>
+      <c r="O4" s="5">
+        <v>12</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3486760047265595</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2341723566992139</v>
+      </c>
+      <c r="R4" s="5">
+        <v>12</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4701477741331399</v>
+        <v>0.8307585074397843</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3988241394119361</v>
+        <v>0.7046536204574316</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3439348721191537</v>
+        <v>0.7176365210506241</v>
       </c>
       <c r="E5" s="4">
-        <v>77.90816326530616</v>
+        <v>75.45787545787545</v>
       </c>
       <c r="F5" s="4">
-        <v>79.5964549991391</v>
+        <v>76.4253140595419</v>
       </c>
       <c r="G5" s="5">
         <v>26</v>
       </c>
       <c r="H5" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -1794,11 +1972,29 @@
         <v>9</v>
       </c>
       <c r="M5" s="5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.3868267229061778</v>
+      </c>
+      <c r="O5" s="5">
+        <v>17</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6704506653305268</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4351174875471017</v>
+      </c>
+      <c r="R5" s="5">
+        <v>16</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2005,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2024,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2066,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,132 +2097,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3337276947333429</v>
+        <v>0.4420283323552955</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3453052220490784</v>
+        <v>0.4589025161898962</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3029761621555889</v>
+        <v>0.3776992357168852</v>
       </c>
       <c r="E3" s="4">
-        <v>79.06724228152798</v>
+        <v>80.94583987441131</v>
       </c>
       <c r="F3" s="4">
-        <v>80.19962140767474</v>
+        <v>83.041645155738</v>
       </c>
       <c r="G3" s="5">
         <v>26</v>
       </c>
       <c r="H3" s="5">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
         <v>2</v>
       </c>
-      <c r="J3" s="5">
-        <v>7</v>
-      </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4379470024558141</v>
+      </c>
+      <c r="O3" s="5">
+        <v>23</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1997316063971983</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.209441718601295</v>
+      </c>
+      <c r="R3" s="5">
+        <v>23</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3743657574228463</v>
+        <v>0.2808989160060182</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2566478193557228</v>
+        <v>0.2713124555258553</v>
       </c>
       <c r="D4" s="4">
-        <v>0.228271181749206</v>
+        <v>0.2541313005330438</v>
       </c>
       <c r="E4" s="4">
-        <v>74.3563579277865</v>
+        <v>80.09157509157504</v>
       </c>
       <c r="F4" s="4">
-        <v>62.93279986232823</v>
+        <v>83.06874892445096</v>
       </c>
       <c r="G4" s="5">
         <v>26</v>
       </c>
       <c r="H4" s="5">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="I4" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2389386144269259</v>
+      </c>
+      <c r="O4" s="5">
+        <v>23</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1843998619148572</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1831593978083852</v>
+      </c>
+      <c r="R4" s="5">
+        <v>23</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2438478163042991</v>
+        <v>0.3140860059165246</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2678248563245668</v>
+        <v>0.3464119540212494</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2219678489904005</v>
+        <v>0.2860096262920347</v>
       </c>
       <c r="E5" s="4">
-        <v>78.0494505494506</v>
+        <v>80.64756671899534</v>
       </c>
       <c r="F5" s="4">
-        <v>79.80166924797786</v>
+        <v>84.93675787299939</v>
       </c>
       <c r="G5" s="5">
         <v>26</v>
       </c>
       <c r="H5" s="5">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.3094736687360622</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2216596045179667</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2432079282462011</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2305,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2313,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2324,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2366,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,34 +2397,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5507671484683254</v>
+        <v>0.36348272752706</v>
       </c>
       <c r="C3" s="4">
-        <v>0.524021753602732</v>
+        <v>0.3334768133515809</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5295599992561484</v>
+        <v>0.294321959698797</v>
       </c>
       <c r="E3" s="4">
-        <v>78.69178440607016</v>
+        <v>79.90973312401886</v>
       </c>
       <c r="F3" s="4">
-        <v>80.87721562553725</v>
+        <v>81.20375150576427</v>
       </c>
       <c r="G3" s="5">
         <v>26</v>
       </c>
       <c r="H3" s="5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" s="5">
         <v>2</v>
@@ -2140,66 +2456,102 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.283056718453156</v>
+      </c>
+      <c r="O3" s="5">
+        <v>20</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3017536489952009</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3164726617539088</v>
+      </c>
+      <c r="R3" s="5">
+        <v>20</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4250192912722027</v>
+        <v>0.3328713566121166</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2117795765325639</v>
+        <v>0.1442794631009039</v>
       </c>
       <c r="D4" s="4">
-        <v>0.223001747623932</v>
+        <v>0.2189784997167036</v>
       </c>
       <c r="E4" s="4">
-        <v>74.18236525379376</v>
+        <v>73.66954474097336</v>
       </c>
       <c r="F4" s="4">
-        <v>64.97633797969506</v>
+        <v>58.69428669764188</v>
       </c>
       <c r="G4" s="5">
         <v>26</v>
       </c>
       <c r="H4" s="5">
+        <v>9</v>
+      </c>
+      <c r="I4" s="5">
         <v>14</v>
       </c>
-      <c r="I4" s="5">
-        <v>7</v>
-      </c>
       <c r="J4" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.01709440367209128</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3433909896410959</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1461788412866919</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4592147264599891</v>
+        <v>0.4701477741331399</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3915708528149701</v>
+        <v>0.3988241394119361</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3878488556262399</v>
+        <v>0.3439348721191537</v>
       </c>
       <c r="E5" s="4">
-        <v>77.4332810047096</v>
+        <v>77.90816326530616</v>
       </c>
       <c r="F5" s="4">
-        <v>79.46222681121998</v>
+        <v>79.5964549991391</v>
       </c>
       <c r="G5" s="5">
         <v>26</v>
@@ -2222,9 +2574,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.2751000650791632</v>
+      </c>
+      <c r="O5" s="5">
+        <v>17</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3842264831766096</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3761846619231249</v>
+      </c>
+      <c r="R5" s="5">
+        <v>17</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2605,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2624,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2666,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,132 +2697,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1706748050796975</v>
+        <v>0.3337276947333429</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1719183772495326</v>
+        <v>0.3453052220490784</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1948203652756481</v>
+        <v>0.3029761621555889</v>
       </c>
       <c r="E3" s="4">
-        <v>73.5230245944532</v>
+        <v>79.06724228152798</v>
       </c>
       <c r="F3" s="4">
-        <v>78.95112717260352</v>
+        <v>80.19962140767474</v>
       </c>
       <c r="G3" s="5">
         <v>26</v>
       </c>
       <c r="H3" s="5">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3247198094273057</v>
+      </c>
+      <c r="O3" s="5">
+        <v>17</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2653339043352411</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.28639179871542</v>
+      </c>
+      <c r="R3" s="5">
+        <v>17</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3390703080289968</v>
+        <v>0.3743657574228463</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3358015785994256</v>
+        <v>0.2566478193557228</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3604389657694826</v>
+        <v>0.228271181749206</v>
       </c>
       <c r="E4" s="4">
-        <v>72.32731554160129</v>
+        <v>74.3563579277865</v>
       </c>
       <c r="F4" s="4">
-        <v>78.85906040268389</v>
+        <v>62.93279986232823</v>
       </c>
       <c r="G4" s="5">
         <v>26</v>
       </c>
       <c r="H4" s="5">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J4" s="5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2275524729201844</v>
+      </c>
+      <c r="O4" s="5">
+        <v>11</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2593220416794085</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2247823207451131</v>
+      </c>
+      <c r="R4" s="5">
+        <v>11</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4518155488180441</v>
+        <v>0.2438478163042991</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4164016214978151</v>
+        <v>0.2678248563245668</v>
       </c>
       <c r="D5" s="4">
-        <v>0.504603874474473</v>
+        <v>0.2219678489904005</v>
       </c>
       <c r="E5" s="4">
-        <v>73.12140240711656</v>
+        <v>78.0494505494506</v>
       </c>
       <c r="F5" s="4">
-        <v>81.07597659610909</v>
+        <v>79.80166924797786</v>
       </c>
       <c r="G5" s="5">
         <v>26</v>
       </c>
       <c r="H5" s="5">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.2361383374108574</v>
+      </c>
+      <c r="O5" s="5">
+        <v>17</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2096119336435967</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2349647399324181</v>
+      </c>
+      <c r="R5" s="5">
+        <v>17</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2905,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2913,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2924,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2966,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,132 +2997,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6564796052866957</v>
+        <v>0.5507671484683254</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6610746861624716</v>
+        <v>0.524021753602732</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6055770667120258</v>
+        <v>0.5295599992561484</v>
       </c>
       <c r="E3" s="4">
-        <v>82.24097331240188</v>
+        <v>78.69178440607016</v>
       </c>
       <c r="F3" s="4">
-        <v>85.29556014455325</v>
+        <v>80.87721562553725</v>
       </c>
       <c r="G3" s="5">
         <v>26</v>
       </c>
       <c r="H3" s="5">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.5228294471813688</v>
+      </c>
+      <c r="O3" s="5">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.307974829695379</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3173901712893414</v>
+      </c>
+      <c r="R3" s="5">
+        <v>21</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7298068278759432</v>
+        <v>0.4250192912722027</v>
       </c>
       <c r="C4" s="4">
-        <v>0.7182818173045193</v>
+        <v>0.2117795765325639</v>
       </c>
       <c r="D4" s="4">
-        <v>0.69874488282265</v>
+        <v>0.223001747623932</v>
       </c>
       <c r="E4" s="4">
-        <v>81.70460491889062</v>
+        <v>74.18236525379376</v>
       </c>
       <c r="F4" s="4">
-        <v>84.14687661331881</v>
+        <v>64.97633797969506</v>
       </c>
       <c r="G4" s="5">
         <v>26</v>
       </c>
       <c r="H4" s="5">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I4" s="5">
+        <v>7</v>
+      </c>
+      <c r="J4" s="5">
+        <v>5</v>
+      </c>
+      <c r="K4" s="5">
         <v>1</v>
       </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1905543571143044</v>
+      </c>
+      <c r="O4" s="5">
+        <v>14</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3139732580679115</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1613890037165417</v>
+      </c>
+      <c r="R4" s="5">
+        <v>14</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5233762215905862</v>
+        <v>0.4592147264599891</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5279342962351145</v>
+        <v>0.3915708528149701</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4754064478321627</v>
+        <v>0.3878488556262399</v>
       </c>
       <c r="E5" s="4">
-        <v>81.35269492412353</v>
+        <v>77.4332810047096</v>
       </c>
       <c r="F5" s="4">
-        <v>83.96016176217496</v>
+        <v>79.46222681121998</v>
       </c>
       <c r="G5" s="5">
         <v>26</v>
       </c>
       <c r="H5" s="5">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.3337420506989922</v>
+      </c>
+      <c r="O5" s="5">
+        <v>17</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3692717848320787</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3236594322907639</v>
+      </c>
+      <c r="R5" s="5">
+        <v>17</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3205,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3213,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3224,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3266,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,132 +3297,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3360750613874644</v>
+        <v>0.1706748050796975</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3792184938066629</v>
+        <v>0.1719183772495326</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3228566801112313</v>
+        <v>0.1948203652756481</v>
       </c>
       <c r="E3" s="4">
-        <v>62.06043956044001</v>
+        <v>73.5230245944532</v>
       </c>
       <c r="F3" s="4">
-        <v>63.84787472035701</v>
+        <v>78.95112717260352</v>
       </c>
       <c r="G3" s="5">
         <v>26</v>
       </c>
       <c r="H3" s="5">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1475301628435601</v>
+      </c>
+      <c r="O3" s="5">
+        <v>21</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1051622870862195</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1204755491495704</v>
+      </c>
+      <c r="R3" s="5">
+        <v>21</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4261622395353841</v>
+        <v>0.3390703080289968</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4010948969014009</v>
+        <v>0.3358015785994256</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4461379245422133</v>
+        <v>0.3604389657694826</v>
       </c>
       <c r="E4" s="4">
-        <v>60.38199895342796</v>
+        <v>72.32731554160129</v>
       </c>
       <c r="F4" s="4">
-        <v>60.36654620547262</v>
+        <v>78.85906040268389</v>
       </c>
       <c r="G4" s="5">
         <v>26</v>
       </c>
       <c r="H4" s="5">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.3358015785994256</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1033895304134274</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1195168117026616</v>
+      </c>
+      <c r="R4" s="5">
+        <v>21</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4463956498947201</v>
+        <v>0.4518155488180441</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4319056786967887</v>
+        <v>0.4164016214978151</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4625657143895139</v>
+        <v>0.504603874474473</v>
       </c>
       <c r="E5" s="4">
-        <v>58.16849816849813</v>
+        <v>73.12140240711656</v>
       </c>
       <c r="F5" s="4">
-        <v>62.88203407330862</v>
+        <v>81.07597659610909</v>
       </c>
       <c r="G5" s="5">
         <v>26</v>
       </c>
       <c r="H5" s="5">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.4164016214978151</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2037117194080481</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1415183573717242</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3505,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3513,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3524,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3566,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,34 +3597,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5357635492882646</v>
+        <v>0.6564796052866957</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5065261420846116</v>
+        <v>0.6610746861624716</v>
       </c>
       <c r="D3" s="4">
-        <v>0.474646166138326</v>
+        <v>0.6055770667120258</v>
       </c>
       <c r="E3" s="4">
-        <v>81.32260596546314</v>
+        <v>82.24097331240188</v>
       </c>
       <c r="F3" s="4">
-        <v>83.16597831698469</v>
+        <v>85.29556014455325</v>
       </c>
       <c r="G3" s="5">
         <v>26</v>
       </c>
       <c r="H3" s="5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>1</v>
@@ -2992,91 +3656,145 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.6610746861624716</v>
+      </c>
+      <c r="O3" s="5">
+        <v>25</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2039834290653128</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2073638821171183</v>
+      </c>
+      <c r="R3" s="5">
+        <v>25</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5096245626492485</v>
+        <v>0.7298068278759432</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5137988693044829</v>
+        <v>0.7182818173045193</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4888057239428826</v>
+        <v>0.69874488282265</v>
       </c>
       <c r="E4" s="4">
-        <v>81.48613291470434</v>
+        <v>81.70460491889062</v>
       </c>
       <c r="F4" s="4">
-        <v>83.91713990707191</v>
+        <v>84.14687661331881</v>
       </c>
       <c r="G4" s="5">
         <v>26</v>
       </c>
       <c r="H4" s="5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.7182818173045193</v>
+      </c>
+      <c r="O4" s="5">
+        <v>24</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1642627819669245</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1577813510159284</v>
+      </c>
+      <c r="R4" s="5">
+        <v>24</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4634071792344257</v>
+        <v>0.5233762215905862</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4795662149195949</v>
+        <v>0.5279342962351145</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3807396977936899</v>
+        <v>0.4754064478321627</v>
       </c>
       <c r="E5" s="4">
-        <v>80.72344322344318</v>
+        <v>81.35269492412353</v>
       </c>
       <c r="F5" s="4">
-        <v>84.52848046807759</v>
+        <v>83.96016176217496</v>
       </c>
       <c r="G5" s="5">
         <v>26</v>
       </c>
       <c r="H5" s="5">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.5279342962351145</v>
+      </c>
+      <c r="O5" s="5">
+        <v>20</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1657937161290077</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1947000790855216</v>
+      </c>
+      <c r="R5" s="5">
+        <v>20</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3805,1470 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.3360750613874644</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3792184938066629</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3228566801112313</v>
+      </c>
+      <c r="E3" s="4">
+        <v>62.06043956044001</v>
+      </c>
+      <c r="F3" s="4">
+        <v>63.84787472035701</v>
+      </c>
+      <c r="G3" s="5">
+        <v>26</v>
+      </c>
+      <c r="H3" s="5">
+        <v>9</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>17</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>17</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.3465771504269733</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.141772237770812</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1819410033159676</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4261622395353841</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.4010948969014009</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.4461379245422133</v>
+      </c>
+      <c r="E4" s="4">
+        <v>60.38199895342796</v>
+      </c>
+      <c r="F4" s="4">
+        <v>60.36654620547262</v>
+      </c>
+      <c r="G4" s="5">
+        <v>26</v>
+      </c>
+      <c r="H4" s="5">
+        <v>9</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>16</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>16</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.4010948969014009</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1822385820919261</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1475092999742005</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.4463956498947201</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.4319056786967887</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.4625657143895139</v>
+      </c>
+      <c r="E5" s="4">
+        <v>58.16849816849813</v>
+      </c>
+      <c r="F5" s="4">
+        <v>62.88203407330862</v>
+      </c>
+      <c r="G5" s="5">
+        <v>26</v>
+      </c>
+      <c r="H5" s="5">
+        <v>9</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>17</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>16</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.09928250239244799</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4005729564828211</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4208742895420723</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.5357635492882646</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.5065261420846116</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.474646166138326</v>
+      </c>
+      <c r="E3" s="4">
+        <v>81.32260596546314</v>
+      </c>
+      <c r="F3" s="4">
+        <v>83.16597831698469</v>
+      </c>
+      <c r="G3" s="5">
+        <v>26</v>
+      </c>
+      <c r="H3" s="5">
+        <v>22</v>
+      </c>
+      <c r="I3" s="5">
+        <v>3</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.5065261420846116</v>
+      </c>
+      <c r="O3" s="5">
+        <v>22</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1725852088682999</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1612316014756965</v>
+      </c>
+      <c r="R3" s="5">
+        <v>22</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.5096245626492485</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.5137988693044829</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.4888057239428826</v>
+      </c>
+      <c r="E4" s="4">
+        <v>81.48613291470434</v>
+      </c>
+      <c r="F4" s="4">
+        <v>83.91713990707191</v>
+      </c>
+      <c r="G4" s="5">
+        <v>26</v>
+      </c>
+      <c r="H4" s="5">
+        <v>22</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.5137988693044829</v>
+      </c>
+      <c r="O4" s="5">
+        <v>22</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1490841299741504</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.165799682219006</v>
+      </c>
+      <c r="R4" s="5">
+        <v>22</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.4634071792344257</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.4795662149195949</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3807396977936899</v>
+      </c>
+      <c r="E5" s="4">
+        <v>80.72344322344318</v>
+      </c>
+      <c r="F5" s="4">
+        <v>84.52848046807759</v>
+      </c>
+      <c r="G5" s="5">
+        <v>26</v>
+      </c>
+      <c r="H5" s="5">
+        <v>23</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.4795662149195949</v>
+      </c>
+      <c r="O5" s="5">
+        <v>23</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1685688188044029</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1722893200478294</v>
+      </c>
+      <c r="R5" s="5">
+        <v>23</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>64.1025641025641</v>
+      </c>
+      <c r="C3" s="3">
+        <v>14.1025641025641</v>
+      </c>
+      <c r="D3" s="3">
+        <v>21.7948717948718</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>21.7948717948718</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.3837650454991754</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.3438572984358784</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.2891232041490918</v>
+      </c>
+      <c r="K3" s="4">
+        <v>73.90066282923428</v>
+      </c>
+      <c r="L3" s="4">
+        <v>71.71499455056401</v>
+      </c>
+      <c r="M3" s="5">
+        <v>78</v>
+      </c>
+      <c r="N3" s="5">
+        <v>617288.8915538788</v>
+      </c>
+      <c r="O3" s="4">
+        <v>31.88805101528457</v>
+      </c>
+      <c r="P3" s="5">
+        <v>19358</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>78.2051282051282</v>
+      </c>
+      <c r="C4" s="3">
+        <v>6.41025641025641</v>
+      </c>
+      <c r="D4" s="3">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.5003899836134057</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.4046161496167733</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.4040335434882695</v>
+      </c>
+      <c r="K4" s="4">
+        <v>80.030525030525</v>
+      </c>
+      <c r="L4" s="4">
+        <v>79.18301497160539</v>
+      </c>
+      <c r="M4" s="5">
+        <v>78</v>
+      </c>
+      <c r="N4" s="5">
+        <v>997707.0710659027</v>
+      </c>
+      <c r="O4" s="4">
+        <v>62.35279489193817</v>
+      </c>
+      <c r="P4" s="5">
+        <v>16001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>82.05128205128204</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2.564102564102564</v>
+      </c>
+      <c r="D5" s="3">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.1517287748674434</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.1602136390044465</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.130388718763867</v>
+      </c>
+      <c r="K5" s="4">
+        <v>78.54962497819639</v>
+      </c>
+      <c r="L5" s="4">
+        <v>80.71932541731142</v>
+      </c>
+      <c r="M5" s="5">
+        <v>78</v>
+      </c>
+      <c r="N5" s="5">
+        <v>2357904.868841171</v>
+      </c>
+      <c r="O5" s="4">
+        <v>145.1822467114815</v>
+      </c>
+      <c r="P5" s="5">
+        <v>16241</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="C6" s="3">
+        <v>8.974358974358974</v>
+      </c>
+      <c r="D6" s="3">
+        <v>24.35897435897436</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>24.35897435897436</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.3087398107588892</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.2996629872826679</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.2847182928808121</v>
+      </c>
+      <c r="K6" s="4">
+        <v>77.70931449502879</v>
+      </c>
+      <c r="L6" s="4">
+        <v>76.12918029025469</v>
+      </c>
+      <c r="M6" s="5">
+        <v>78</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1442456.951379776</v>
+      </c>
+      <c r="O6" s="4">
+        <v>84.00541327702382</v>
+      </c>
+      <c r="P6" s="5">
+        <v>17171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>88.46153846153845</v>
+      </c>
+      <c r="C7" s="3">
+        <v>3.846153846153846</v>
+      </c>
+      <c r="D7" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1.282051282051282</v>
+      </c>
+      <c r="F7" s="3">
+        <v>6.41025641025641</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.1776025405994033</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.1790003930528283</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.1656261689391237</v>
+      </c>
+      <c r="K7" s="4">
+        <v>83.56924821210529</v>
+      </c>
+      <c r="L7" s="4">
+        <v>85.74155337578141</v>
+      </c>
+      <c r="M7" s="5">
+        <v>78</v>
+      </c>
+      <c r="N7" s="5">
+        <v>3639257.705688477</v>
+      </c>
+      <c r="O7" s="4">
+        <v>275.8476241710359</v>
+      </c>
+      <c r="P7" s="5">
+        <v>13193</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>55.12820512820513</v>
+      </c>
+      <c r="C8" s="3">
+        <v>20.51282051282051</v>
+      </c>
+      <c r="D8" s="3">
+        <v>24.35897435897436</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>24.35897435897436</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.3834382903301186</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.3668889926444793</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.314221175993233</v>
+      </c>
+      <c r="K8" s="4">
+        <v>77.20652363509512</v>
+      </c>
+      <c r="L8" s="4">
+        <v>71.48511443813362</v>
+      </c>
+      <c r="M8" s="5">
+        <v>78</v>
+      </c>
+      <c r="N8" s="5">
+        <v>318031.3701629639</v>
+      </c>
+      <c r="O8" s="4">
+        <v>17.26929681597328</v>
+      </c>
+      <c r="P8" s="5">
+        <v>18416</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>56.41025641025641</v>
+      </c>
+      <c r="C9" s="3">
+        <v>19.23076923076923</v>
+      </c>
+      <c r="D9" s="3">
+        <v>24.35897435897436</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1.282051282051282</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.4711389946233979</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.3139339612644628</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.3607760420306509</v>
+      </c>
+      <c r="K9" s="4">
+        <v>75.0959358102215</v>
+      </c>
+      <c r="L9" s="4">
+        <v>72.41051454138773</v>
+      </c>
+      <c r="M9" s="5">
+        <v>78</v>
+      </c>
+      <c r="N9" s="5">
+        <v>568048.7802028656</v>
+      </c>
+      <c r="O9" s="4">
+        <v>31.11402641194422</v>
+      </c>
+      <c r="P9" s="5">
+        <v>18257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>85.8974358974359</v>
+      </c>
+      <c r="C10" s="3">
+        <v>3.846153846153846</v>
+      </c>
+      <c r="D10" s="3">
+        <v>10.25641025641026</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1.282051282051282</v>
+      </c>
+      <c r="F10" s="3">
+        <v>8.974358974358974</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.2019303576100074</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.211002868217804</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.2168995093393695</v>
+      </c>
+      <c r="K10" s="4">
+        <v>80.56166056166056</v>
+      </c>
+      <c r="L10" s="4">
+        <v>83.68238398439874</v>
+      </c>
+      <c r="M10" s="5">
+        <v>78</v>
+      </c>
+      <c r="N10" s="5">
+        <v>1544588.921546936</v>
+      </c>
+      <c r="O10" s="4">
+        <v>105.670720499893</v>
+      </c>
+      <c r="P10" s="5">
+        <v>14617</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>58.97435897435898</v>
+      </c>
+      <c r="C11" s="3">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="D11" s="3">
+        <v>17.94871794871795</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>17.94871794871795</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.3431237072709688</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.3052217838989463</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.2677798819136805</v>
+      </c>
+      <c r="K11" s="4">
+        <v>77.16248037676608</v>
+      </c>
+      <c r="L11" s="4">
+        <v>73.16483106751437</v>
+      </c>
+      <c r="M11" s="5">
+        <v>78</v>
+      </c>
+      <c r="N11" s="5">
+        <v>730849.4210243225</v>
+      </c>
+      <c r="O11" s="4">
+        <v>41.77237202928227</v>
+      </c>
+      <c r="P11" s="5">
+        <v>17496</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>57.69230769230769</v>
+      </c>
+      <c r="C12" s="3">
+        <v>11.53846153846154</v>
+      </c>
+      <c r="D12" s="3">
+        <v>30.76923076923077</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1.282051282051282</v>
+      </c>
+      <c r="F12" s="3">
+        <v>29.48717948717949</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.2447559598860821</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.2519037041157665</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.2080622592051521</v>
+      </c>
+      <c r="K12" s="4">
+        <v>77.15768358625499</v>
+      </c>
+      <c r="L12" s="4">
+        <v>74.31136350599418</v>
+      </c>
+      <c r="M12" s="5">
+        <v>78</v>
+      </c>
+      <c r="N12" s="5">
+        <v>398618.8523769379</v>
+      </c>
+      <c r="O12" s="4">
+        <v>22.99105158478128</v>
+      </c>
+      <c r="P12" s="5">
+        <v>17338</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="C13" s="3">
+        <v>12.82051282051282</v>
+      </c>
+      <c r="D13" s="3">
+        <v>20.51282051282051</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1.282051282051282</v>
+      </c>
+      <c r="F13" s="3">
+        <v>19.23076923076923</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.3304066241984565</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.2774394230394374</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.2758973232702097</v>
+      </c>
+      <c r="K13" s="4">
+        <v>76.76914355485782</v>
+      </c>
+      <c r="L13" s="4">
+        <v>75.10526013881827</v>
+      </c>
+      <c r="M13" s="5">
+        <v>78</v>
+      </c>
+      <c r="N13" s="5">
+        <v>1307735.147953033</v>
+      </c>
+      <c r="O13" s="4">
+        <v>75.70540395698931</v>
+      </c>
+      <c r="P13" s="5">
+        <v>17274</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>80.76923076923077</v>
+      </c>
+      <c r="C14" s="3">
+        <v>3.846153846153846</v>
+      </c>
+      <c r="D14" s="3">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2.564102564102564</v>
+      </c>
+      <c r="F14" s="3">
+        <v>12.82051282051282</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.1374211789692317</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.1271702394079854</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.1616859992867923</v>
+      </c>
+      <c r="K14" s="4">
+        <v>72.99058084772372</v>
+      </c>
+      <c r="L14" s="4">
+        <v>79.62872139046645</v>
+      </c>
+      <c r="M14" s="5">
+        <v>78</v>
+      </c>
+      <c r="N14" s="5">
+        <v>8082852.641820908</v>
+      </c>
+      <c r="O14" s="4">
+        <v>385.9821709479446</v>
+      </c>
+      <c r="P14" s="5">
+        <v>20941</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>88.46153846153845</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1.282051282051282</v>
+      </c>
+      <c r="D15" s="3">
+        <v>10.25641025641026</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>10.25641025641026</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.1780133090537483</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.186447116797401</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.1710054466855397</v>
+      </c>
+      <c r="K15" s="4">
+        <v>81.76609105180536</v>
+      </c>
+      <c r="L15" s="4">
+        <v>84.4675328400141</v>
+      </c>
+      <c r="M15" s="5">
+        <v>78</v>
+      </c>
+      <c r="N15" s="5">
+        <v>5334886.476993561</v>
+      </c>
+      <c r="O15" s="4">
+        <v>387.0066359806718</v>
+      </c>
+      <c r="P15" s="5">
+        <v>13785</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>34.61538461538461</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1.282051282051282</v>
+      </c>
+      <c r="D16" s="3">
+        <v>64.1025641025641</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1.282051282051282</v>
+      </c>
+      <c r="F16" s="3">
+        <v>62.82051282051282</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.2415279254485197</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.2501081976107468</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.2438506887528057</v>
+      </c>
+      <c r="K16" s="4">
+        <v>60.20364556078847</v>
+      </c>
+      <c r="L16" s="4">
+        <v>62.36548499971209</v>
+      </c>
+      <c r="M16" s="5">
+        <v>78</v>
+      </c>
+      <c r="N16" s="5">
+        <v>2035709.21254158</v>
+      </c>
+      <c r="O16" s="4">
+        <v>101.1985092732939</v>
+      </c>
+      <c r="P16" s="5">
+        <v>20116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>85.8974358974359</v>
+      </c>
+      <c r="C17" s="3">
+        <v>6.41025641025641</v>
+      </c>
+      <c r="D17" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.1634127192156178</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.1665275015281124</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.1667403100032755</v>
+      </c>
+      <c r="K17" s="4">
+        <v>81.17739403453689</v>
+      </c>
+      <c r="L17" s="4">
+        <v>83.87053289737807</v>
+      </c>
+      <c r="M17" s="5">
+        <v>78</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1380213.397741318</v>
+      </c>
+      <c r="O17" s="4">
+        <v>102.5037800030685</v>
+      </c>
+      <c r="P17" s="5">
+        <v>13465</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3523,7 +5699,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="25" customHeight="1">
@@ -3611,7 +5787,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25" customHeight="1">
@@ -3693,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M14" s="5">
         <v>0</v>
@@ -3787,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="5">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -3847,9 +6023,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>50</v>
+      </c>
+      <c r="C3" s="5">
+        <v>11</v>
+      </c>
+      <c r="D3" s="5">
+        <v>17</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>17</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>8</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>61</v>
+      </c>
+      <c r="C4" s="5">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5">
+        <v>12</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>12</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>8</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>64</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5">
+        <v>12</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>12</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>6</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>52</v>
+      </c>
+      <c r="C6" s="5">
+        <v>7</v>
+      </c>
+      <c r="D6" s="5">
+        <v>19</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>19</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>9</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>69</v>
+      </c>
+      <c r="C7" s="5">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5">
+        <v>6</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5">
+        <v>5</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>5</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>43</v>
+      </c>
+      <c r="C8" s="5">
+        <v>16</v>
+      </c>
+      <c r="D8" s="5">
+        <v>19</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>19</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>10</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>44</v>
+      </c>
+      <c r="C9" s="5">
+        <v>15</v>
+      </c>
+      <c r="D9" s="5">
+        <v>19</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>18</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>10</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>67</v>
+      </c>
+      <c r="C10" s="5">
+        <v>3</v>
+      </c>
+      <c r="D10" s="5">
+        <v>8</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5">
+        <v>7</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5">
+        <v>1</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>5</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46</v>
+      </c>
+      <c r="C11" s="5">
+        <v>18</v>
+      </c>
+      <c r="D11" s="5">
+        <v>14</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>14</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>9</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>45</v>
+      </c>
+      <c r="C12" s="5">
+        <v>9</v>
+      </c>
+      <c r="D12" s="5">
+        <v>24</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5">
+        <v>23</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5">
+        <v>1</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>9</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>52</v>
+      </c>
+      <c r="C13" s="5">
+        <v>10</v>
+      </c>
+      <c r="D13" s="5">
+        <v>16</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5">
+        <v>15</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5">
+        <v>1</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>9</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>63</v>
+      </c>
+      <c r="C14" s="5">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5">
+        <v>12</v>
+      </c>
+      <c r="E14" s="5">
+        <v>2</v>
+      </c>
+      <c r="F14" s="5">
+        <v>10</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>2</v>
+      </c>
+      <c r="I14" s="5">
+        <v>2</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>5</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>69</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5">
+        <v>8</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>8</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>5</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>27</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5">
+        <v>50</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5">
+        <v>49</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>25</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>67</v>
+      </c>
+      <c r="C17" s="5">
+        <v>5</v>
+      </c>
+      <c r="D17" s="5">
+        <v>6</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>6</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>3</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6791,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6833,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,10 +6864,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3316505487534191</v>
@@ -3960,10 +6923,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2404038456704058</v>
+      </c>
+      <c r="O3" s="5">
+        <v>20</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3554391009321333</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4211329924566243</v>
+      </c>
+      <c r="R3" s="5">
+        <v>20</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.3459159805097946</v>
@@ -4001,10 +6982,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2850307665899287</v>
+      </c>
+      <c r="O4" s="5">
+        <v>13</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.366621543079703</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1676928517708513</v>
+      </c>
+      <c r="R4" s="5">
+        <v>13</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.4333052739640751</v>
@@ -4042,9 +7041,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.01488648179942482</v>
+      </c>
+      <c r="O5" s="5">
+        <v>17</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.42923449248569</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3876587058611982</v>
+      </c>
+      <c r="R5" s="5">
+        <v>17</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7072,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7091,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7133,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,10 +7164,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.4044851804750067</v>
@@ -4173,17 +7223,33 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.05229223347108898</v>
+      </c>
+      <c r="O3" s="5">
+        <v>23</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3776185081397937</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.349941793649776</v>
+      </c>
+      <c r="R3" s="5">
+        <v>23</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>3.269347596796647</v>
       </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
         <v>3.491959639401913</v>
       </c>
@@ -4214,10 +7280,28 @@
       <c r="M4" s="5">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>3.439347609854036</v>
+      </c>
+      <c r="O4" s="5">
+        <v>17</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6208901458356597</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5366978596479697</v>
+      </c>
+      <c r="R4" s="5">
+        <v>17</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.6290532900783341</v>
@@ -4255,9 +7339,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.262058003727234</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5026612968647636</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3575742980315636</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7370,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7389,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7431,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,10 +7462,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3530559087625617</v>
@@ -4386,10 +7521,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3622108534729467</v>
+      </c>
+      <c r="O3" s="5">
+        <v>23</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1753295810090787</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1858595972170483</v>
+      </c>
+      <c r="R3" s="5">
+        <v>23</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.3130979171814178</v>
@@ -4427,10 +7580,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.31724027661393</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1155648971593931</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1193822845728747</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.2506653337474041</v>
@@ -4468,9 +7639,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.2705760760106868</v>
+      </c>
+      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1642918464338582</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1710122128016652</v>
+      </c>
+      <c r="R5" s="5">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7670,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7689,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7731,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,10 +7762,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3737137477588069</v>
@@ -4599,10 +7821,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1944142705681315</v>
+      </c>
+      <c r="O3" s="5">
+        <v>18</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2966415665985774</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2807180677073878</v>
+      </c>
+      <c r="R3" s="5">
+        <v>18</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2370249099262087</v>
@@ -4640,10 +7880,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.0158186446701115</v>
+      </c>
+      <c r="O4" s="5">
+        <v>18</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.232841536041673</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2125638412654584</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.3889905661658676</v>
@@ -4681,9 +7939,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.06380739960330217</v>
+      </c>
+      <c r="O5" s="5">
+        <v>16</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3967363296364173</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4189625610742187</v>
+      </c>
+      <c r="R5" s="5">
+        <v>16</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7970,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7989,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8031,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,10 +8062,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3056836223636813</v>
@@ -4812,10 +8121,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3055027508417766</v>
+      </c>
+      <c r="O3" s="5">
+        <v>25</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.19454451114002</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1981830605479936</v>
+      </c>
+      <c r="R3" s="5">
+        <v>25</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.1958856619599116</v>
@@ -4853,10 +8180,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1416396956646238</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1243892562109465</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1183683590635831</v>
+      </c>
+      <c r="R4" s="5">
+        <v>21</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.291461714514939</v>
@@ -4894,9 +8239,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.2497083249113999</v>
+      </c>
+      <c r="O5" s="5">
+        <v>23</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2138738544472435</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2135093507221772</v>
+      </c>
+      <c r="R5" s="5">
+        <v>23</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8270,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.3583712080443892</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3904232196406178</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2895297071355322</v>
-      </c>
-      <c r="E3" s="4">
-        <v>80.03924646781792</v>
-      </c>
-      <c r="F3" s="4">
-        <v>80.37299948373717</v>
-      </c>
-      <c r="G3" s="5">
-        <v>26</v>
-      </c>
-      <c r="H3" s="5">
-        <v>21</v>
-      </c>
-      <c r="I3" s="5">
-        <v>2</v>
-      </c>
-      <c r="J3" s="5">
-        <v>3</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>3</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3019225004519022</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1277013582434586</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2707822085099846</v>
-      </c>
-      <c r="E4" s="4">
-        <v>73.06384092098375</v>
-      </c>
-      <c r="F4" s="4">
-        <v>55.01290655653083</v>
-      </c>
-      <c r="G4" s="5">
-        <v>26</v>
-      </c>
-      <c r="H4" s="5">
-        <v>7</v>
-      </c>
-      <c r="I4" s="5">
-        <v>14</v>
-      </c>
-      <c r="J4" s="5">
-        <v>5</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>5</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.4996627554989069</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2724021460357266</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3250057131415533</v>
-      </c>
-      <c r="E5" s="4">
-        <v>78.51648351648348</v>
-      </c>
-      <c r="F5" s="4">
-        <v>79.06943727413505</v>
-      </c>
-      <c r="G5" s="5">
-        <v>26</v>
-      </c>
-      <c r="H5" s="5">
-        <v>14</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>12</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>11</v>
-      </c>
-      <c r="M5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.5344161811945386</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.4953863156943257</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.4649490767962513</v>
-      </c>
-      <c r="E3" s="4">
-        <v>76.72161172161171</v>
-      </c>
-      <c r="F3" s="4">
-        <v>76.82369643779039</v>
-      </c>
-      <c r="G3" s="5">
-        <v>26</v>
-      </c>
-      <c r="H3" s="5">
-        <v>16</v>
-      </c>
-      <c r="I3" s="5">
-        <v>5</v>
-      </c>
-      <c r="J3" s="5">
-        <v>5</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>5</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.5497790542897139</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.6241584252035276</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.5650815778010099</v>
-      </c>
-      <c r="E4" s="4">
-        <v>73.10832025117739</v>
-      </c>
-      <c r="F4" s="4">
-        <v>63.9825331268292</v>
-      </c>
-      <c r="G4" s="5">
-        <v>26</v>
-      </c>
-      <c r="H4" s="5">
-        <v>12</v>
-      </c>
-      <c r="I4" s="5">
-        <v>10</v>
-      </c>
-      <c r="J4" s="5">
-        <v>4</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>4</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.8307585074397843</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.7046536204574316</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.7176365210506241</v>
-      </c>
-      <c r="E5" s="4">
-        <v>75.45787545787545</v>
-      </c>
-      <c r="F5" s="4">
-        <v>76.4253140595419</v>
-      </c>
-      <c r="G5" s="5">
-        <v>26</v>
-      </c>
-      <c r="H5" s="5">
-        <v>16</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>10</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>9</v>
-      </c>
-      <c r="M5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/ShiLong-term2021.xlsx
+++ b/public/downloads/ShiLong-term2021.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3133568264969859</v>
+        <v>-0.1365205168054899</v>
       </c>
       <c r="O3" s="5">
         <v>21</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3670391123904735</v>
+        <v>0.318656173511049</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4087520575500589</v>
+        <v>0.3572487316775456</v>
       </c>
       <c r="R3" s="5">
         <v>21</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.02304068856405931</v>
+        <v>0.0173223956073798</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3140389522172002</v>
+        <v>0.3105200027053974</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1233324178772955</v>
+        <v>0.1225155188834842</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -1675,22 +1675,22 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2347413421850638</v>
+        <v>-0.09520644324283012</v>
       </c>
       <c r="O5" s="5">
         <v>15</v>
       </c>
       <c r="P5" s="4">
-        <v>0.469236806382682</v>
+        <v>0.4597576211349279</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4219404366680202</v>
+        <v>0.266297213104644</v>
       </c>
       <c r="R5" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1857,16 +1857,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3149463918230921</v>
+        <v>0.3888527636004824</v>
       </c>
       <c r="O3" s="5">
         <v>16</v>
       </c>
       <c r="P3" s="4">
-        <v>0.394290313813107</v>
+        <v>0.4090204357662405</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2525716384057608</v>
+        <v>0.24091841988281</v>
       </c>
       <c r="R3" s="5">
         <v>16</v>
@@ -1916,16 +1916,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.6146466796270431</v>
+        <v>0.5438518532598664</v>
       </c>
       <c r="O4" s="5">
         <v>12</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3486760047265595</v>
+        <v>0.3233543169891806</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2341723566992139</v>
+        <v>0.2256975090624943</v>
       </c>
       <c r="R4" s="5">
         <v>12</v>
@@ -1975,16 +1975,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3868267229061778</v>
+        <v>0.6977714086827973</v>
       </c>
       <c r="O5" s="5">
         <v>17</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6704506653305268</v>
+        <v>0.6932869791646615</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4351174875471017</v>
+        <v>0.3535122559082104</v>
       </c>
       <c r="R5" s="5">
         <v>16</v>
@@ -2157,16 +2157,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4379470024558141</v>
+        <v>-0.390914005884559</v>
       </c>
       <c r="O3" s="5">
         <v>23</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1997316063971983</v>
+        <v>0.1935108642161716</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.209441718601295</v>
+        <v>0.2048506936306341</v>
       </c>
       <c r="R3" s="5">
         <v>23</v>
@@ -2216,16 +2216,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2389386144269259</v>
+        <v>-0.2820413792716909</v>
       </c>
       <c r="O4" s="5">
         <v>23</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1843998619148572</v>
+        <v>0.1815573964287085</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1831593978083852</v>
+        <v>0.1780721427003577</v>
       </c>
       <c r="R4" s="5">
         <v>23</v>
@@ -2275,16 +2275,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3094736687360622</v>
+        <v>-0.3110603286450093</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2216596045179667</v>
+        <v>0.2218344844133345</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2432079282462011</v>
+        <v>0.2430466700430977</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -2457,16 +2457,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.283056718453156</v>
+        <v>-0.1377247684375789</v>
       </c>
       <c r="O3" s="5">
         <v>20</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3017536489952009</v>
+        <v>0.2954223966947171</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3164726617539088</v>
+        <v>0.2820276252187682</v>
       </c>
       <c r="R3" s="5">
         <v>20</v>
@@ -2516,16 +2516,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.01709440367209128</v>
+        <v>-0.003130634235958496</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3433909896410959</v>
+        <v>0.3309756477433592</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1461788412866919</v>
+        <v>0.1439316148524641</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -2575,16 +2575,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2751000650791632</v>
+        <v>-0.1426977369311544</v>
       </c>
       <c r="O5" s="5">
         <v>17</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3842264831766096</v>
+        <v>0.3986281530769374</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3761846619231249</v>
+        <v>0.3610967475321779</v>
       </c>
       <c r="R5" s="5">
         <v>17</v>
@@ -2757,16 +2757,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3247198094273057</v>
+        <v>-0.2177123277637065</v>
       </c>
       <c r="O3" s="5">
         <v>17</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2653339043352411</v>
+        <v>0.2481434758443474</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.28639179871542</v>
+        <v>0.2663951128860296</v>
       </c>
       <c r="R3" s="5">
         <v>17</v>
@@ -2816,16 +2816,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2275524729201844</v>
+        <v>-0.07868008581795038</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2593220416794085</v>
+        <v>0.3165806521033447</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2247823207451131</v>
+        <v>0.2112484673721827</v>
       </c>
       <c r="R4" s="5">
         <v>11</v>
@@ -2875,16 +2875,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2361383374108574</v>
+        <v>-0.1256500357104642</v>
       </c>
       <c r="O5" s="5">
         <v>17</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2096119336435967</v>
+        <v>0.1932728179447058</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2349647399324181</v>
+        <v>0.219969208869486</v>
       </c>
       <c r="R5" s="5">
         <v>17</v>
@@ -3057,16 +3057,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5228294471813688</v>
+        <v>-0.3919038051539019</v>
       </c>
       <c r="O3" s="5">
         <v>21</v>
       </c>
       <c r="P3" s="4">
-        <v>0.307974829695379</v>
+        <v>0.2855137642277638</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3173901712893414</v>
+        <v>0.2833466787090813</v>
       </c>
       <c r="R3" s="5">
         <v>21</v>
@@ -3116,16 +3116,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1905543571143044</v>
+        <v>-0.140287542192425</v>
       </c>
       <c r="O4" s="5">
         <v>14</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3139732580679115</v>
+        <v>0.3301915715264512</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1613890037165417</v>
+        <v>0.1556038609096301</v>
       </c>
       <c r="R4" s="5">
         <v>14</v>
@@ -3175,16 +3175,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3337420506989922</v>
+        <v>-0.2350416900464438</v>
       </c>
       <c r="O5" s="5">
         <v>17</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3692717848320787</v>
+        <v>0.3590763670612926</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3236594322907639</v>
+        <v>0.3022605368382354</v>
       </c>
       <c r="R5" s="5">
         <v>17</v>
@@ -3357,16 +3357,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1475301628435601</v>
+        <v>0.1304785054701232</v>
       </c>
       <c r="O3" s="5">
         <v>21</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1051622870862195</v>
+        <v>0.1046006398814339</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1204755491495704</v>
+        <v>0.1182477645545911</v>
       </c>
       <c r="R3" s="5">
         <v>21</v>
@@ -3416,16 +3416,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3358015785994256</v>
+        <v>0.3356684706764099</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1033895304134274</v>
+        <v>0.1033997694844286</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1195168117026616</v>
+        <v>0.1195104732301371</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -3475,16 +3475,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4164016214978151</v>
+        <v>0.3741714983545714</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2037117194080481</v>
+        <v>0.2004632483970293</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1415183573717242</v>
+        <v>0.1395073991268079</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -3657,16 +3657,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6610746861624716</v>
+        <v>-0.5800228452214924</v>
       </c>
       <c r="O3" s="5">
         <v>25</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2039834290653128</v>
+        <v>0.187863989573297</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2073638821171183</v>
+        <v>0.1938417386830611</v>
       </c>
       <c r="R3" s="5">
         <v>25</v>
@@ -3716,16 +3716,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.7182818173045193</v>
+        <v>-0.6321757239465668</v>
       </c>
       <c r="O4" s="5">
         <v>24</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1642627819669245</v>
+        <v>0.1509890667116979</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1577813510159284</v>
+        <v>0.1434014928227662</v>
       </c>
       <c r="R4" s="5">
         <v>24</v>
@@ -3775,16 +3775,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.5279342962351145</v>
+        <v>-0.4911249734235597</v>
       </c>
       <c r="O5" s="5">
         <v>20</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1657937161290077</v>
+        <v>0.1602035103487137</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1947000790855216</v>
+        <v>0.191113743852295</v>
       </c>
       <c r="R5" s="5">
         <v>20</v>
@@ -3957,16 +3957,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3465771504269733</v>
+        <v>0.3729533822710209</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.141772237770812</v>
+        <v>0.1438011786818926</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1819410033159676</v>
+        <v>0.1790103108888512</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -4016,16 +4016,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4010948969014009</v>
+        <v>0.3790566045567676</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1822385820919261</v>
+        <v>0.1847909581524297</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1475092999742005</v>
+        <v>0.1441282161452495</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -4075,16 +4075,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.09928250239244799</v>
+        <v>0.1985283001886842</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4005729564828211</v>
+        <v>0.354767203653789</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4208742895420723</v>
+        <v>0.4098469786758238</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -4257,16 +4257,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5065261420846116</v>
+        <v>-0.465937609898436</v>
       </c>
       <c r="O3" s="5">
         <v>22</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1725852088682999</v>
+        <v>0.1721731904879828</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1612316014756965</v>
+        <v>0.1570548041002149</v>
       </c>
       <c r="R3" s="5">
         <v>22</v>
@@ -4316,16 +4316,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.5137988693044829</v>
+        <v>-0.4964265582486824</v>
       </c>
       <c r="O4" s="5">
         <v>22</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1490841299741504</v>
+        <v>0.1462490518911162</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.165799682219006</v>
+        <v>0.1637777381855824</v>
       </c>
       <c r="R4" s="5">
         <v>22</v>
@@ -4375,16 +4375,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4795662149195949</v>
+        <v>-0.4558710926486924</v>
       </c>
       <c r="O5" s="5">
         <v>23</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1685688188044029</v>
+        <v>0.164466617775159</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1722893200478294</v>
+        <v>0.1707427174414105</v>
       </c>
       <c r="R5" s="5">
         <v>23</v>
@@ -4521,13 +4521,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.3837650454991754</v>
+        <v>0.3665167993351143</v>
       </c>
       <c r="I3" s="4">
-        <v>0.3438572984358784</v>
+        <v>0.311416389128832</v>
       </c>
       <c r="J3" s="4">
-        <v>0.2891232041490918</v>
+        <v>0.2730554242222587</v>
       </c>
       <c r="K3" s="4">
         <v>73.90066282923428</v>
@@ -4553,13 +4553,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="3">
-        <v>78.2051282051282</v>
+        <v>76.92307692307693</v>
       </c>
       <c r="C4" s="3">
         <v>6.41025641025641</v>
       </c>
       <c r="D4" s="3">
-        <v>15.38461538461539</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
@@ -4568,16 +4568,16 @@
         <v>15.38461538461539</v>
       </c>
       <c r="G4" s="3">
-        <v>0</v>
+        <v>1.282051282051282</v>
       </c>
       <c r="H4" s="4">
-        <v>0.5003899836134057</v>
+        <v>0.465321161157764</v>
       </c>
       <c r="I4" s="4">
-        <v>0.4046161496167733</v>
+        <v>0.3375423787710294</v>
       </c>
       <c r="J4" s="4">
-        <v>0.4040335434882695</v>
+        <v>0.3982578558323749</v>
       </c>
       <c r="K4" s="4">
         <v>80.030525030525</v>
@@ -4621,13 +4621,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.1517287748674434</v>
+        <v>0.1451199644656793</v>
       </c>
       <c r="I5" s="4">
-        <v>0.1602136390044465</v>
+        <v>0.1567229192763993</v>
       </c>
       <c r="J5" s="4">
-        <v>0.130388718763867</v>
+        <v>0.1266585053496851</v>
       </c>
       <c r="K5" s="4">
         <v>78.54962497819639</v>
@@ -4671,13 +4671,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.3087398107588892</v>
+        <v>0.3127356268139064</v>
       </c>
       <c r="I6" s="4">
-        <v>0.2996629872826679</v>
+        <v>0.2815562350165379</v>
       </c>
       <c r="J6" s="4">
-        <v>0.2847182928808121</v>
+        <v>0.2929454627811583</v>
       </c>
       <c r="K6" s="4">
         <v>77.70931449502879</v>
@@ -4721,13 +4721,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.1776025405994033</v>
+        <v>0.1686461978836171</v>
       </c>
       <c r="I7" s="4">
-        <v>0.1790003930528283</v>
+        <v>0.1644907571342923</v>
       </c>
       <c r="J7" s="4">
-        <v>0.1656261689391237</v>
+        <v>0.1564452792658251</v>
       </c>
       <c r="K7" s="4">
         <v>83.56924821210529</v>
@@ -4753,13 +4753,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="3">
-        <v>55.12820512820513</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="C8" s="3">
         <v>20.51282051282051</v>
       </c>
       <c r="D8" s="3">
-        <v>24.35897435897436</v>
+        <v>25.64102564102564</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
@@ -4768,16 +4768,16 @@
         <v>24.35897435897436</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
+        <v>1.282051282051282</v>
       </c>
       <c r="H8" s="4">
-        <v>0.3834382903301186</v>
+        <v>0.3629779324504581</v>
       </c>
       <c r="I8" s="4">
-        <v>0.3668889926444793</v>
+        <v>0.2878093566875681</v>
       </c>
       <c r="J8" s="4">
-        <v>0.314221175993233</v>
+        <v>0.273361408796209</v>
       </c>
       <c r="K8" s="4">
         <v>77.20652363509512</v>
@@ -4821,13 +4821,13 @@
         <v>1.282051282051282</v>
       </c>
       <c r="H9" s="4">
-        <v>0.4711389946233979</v>
+        <v>0.4752205773066942</v>
       </c>
       <c r="I9" s="4">
-        <v>0.3139339612644628</v>
+        <v>0.2777104754865059</v>
       </c>
       <c r="J9" s="4">
-        <v>0.3607760420306509</v>
+        <v>0.3711226384475252</v>
       </c>
       <c r="K9" s="4">
         <v>75.0959358102215</v>
@@ -4871,13 +4871,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.2019303576100074</v>
+        <v>0.1989675816860715</v>
       </c>
       <c r="I10" s="4">
-        <v>0.211002868217804</v>
+        <v>0.2076299299480278</v>
       </c>
       <c r="J10" s="4">
-        <v>0.2168995093393695</v>
+        <v>0.2177917396548453</v>
       </c>
       <c r="K10" s="4">
         <v>80.56166056166056</v>
@@ -4921,13 +4921,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.3431237072709688</v>
+        <v>0.3416753991716712</v>
       </c>
       <c r="I11" s="4">
-        <v>0.3052217838989463</v>
+        <v>0.2842300379585775</v>
       </c>
       <c r="J11" s="4">
-        <v>0.2677798819136805</v>
+        <v>0.2603826261796244</v>
       </c>
       <c r="K11" s="4">
         <v>77.16248037676608</v>
@@ -4971,13 +4971,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.2447559598860821</v>
+        <v>0.2526656486307993</v>
       </c>
       <c r="I12" s="4">
-        <v>0.2519037041157665</v>
+        <v>0.2353761469097284</v>
       </c>
       <c r="J12" s="4">
-        <v>0.2080622592051521</v>
+        <v>0.193661514378198</v>
       </c>
       <c r="K12" s="4">
         <v>77.15768358625499</v>
@@ -5021,13 +5021,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.3304066241984565</v>
+        <v>0.3249272342718359</v>
       </c>
       <c r="I13" s="4">
-        <v>0.2774394230394374</v>
+        <v>0.2551377583052987</v>
       </c>
       <c r="J13" s="4">
-        <v>0.2758973232702097</v>
+        <v>0.2672286788309799</v>
       </c>
       <c r="K13" s="4">
         <v>76.76914355485782</v>
@@ -5071,13 +5071,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.1374211789692317</v>
+        <v>0.1361545525876306</v>
       </c>
       <c r="I14" s="4">
-        <v>0.1271702394079854</v>
+        <v>0.1257552123038453</v>
       </c>
       <c r="J14" s="4">
-        <v>0.1616859992867923</v>
+        <v>0.1635520243222583</v>
       </c>
       <c r="K14" s="4">
         <v>72.99058084772372</v>
@@ -5121,13 +5121,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.1780133090537483</v>
+        <v>0.1663521888779029</v>
       </c>
       <c r="I15" s="4">
-        <v>0.186447116797401</v>
+        <v>0.1755065822009973</v>
       </c>
       <c r="J15" s="4">
-        <v>0.1710054466855397</v>
+        <v>0.151511435329173</v>
       </c>
       <c r="K15" s="4">
         <v>81.76609105180536</v>
@@ -5171,13 +5171,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.2415279254485197</v>
+        <v>0.2277864468293704</v>
       </c>
       <c r="I16" s="4">
-        <v>0.2501081976107468</v>
+        <v>0.2443285019033082</v>
       </c>
       <c r="J16" s="4">
-        <v>0.2438506887528057</v>
+        <v>0.2304022200679657</v>
       </c>
       <c r="K16" s="4">
         <v>60.20364556078847</v>
@@ -5221,13 +5221,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.1634127192156178</v>
+        <v>0.1609629533847527</v>
       </c>
       <c r="I17" s="4">
-        <v>0.1665275015281124</v>
+        <v>0.1639611706185072</v>
       </c>
       <c r="J17" s="4">
-        <v>0.1667403100032755</v>
+        <v>0.1590016411736417</v>
       </c>
       <c r="K17" s="4">
         <v>81.17739403453689</v>
@@ -6154,13 +6154,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="5">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C4" s="5">
         <v>5</v>
       </c>
       <c r="D4" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="5">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>12</v>
       </c>
       <c r="G4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="5">
         <v>0</v>
@@ -6330,13 +6330,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="5">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C8" s="5">
         <v>16</v>
       </c>
       <c r="D8" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" s="5">
         <v>0</v>
@@ -6345,7 +6345,7 @@
         <v>19</v>
       </c>
       <c r="G8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="5">
         <v>0</v>
@@ -6924,16 +6924,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2404038456704058</v>
+        <v>-0.0978517459408863</v>
       </c>
       <c r="O3" s="5">
         <v>20</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3554391009321333</v>
+        <v>0.3066106156912029</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4211329924566243</v>
+        <v>0.3637063367901277</v>
       </c>
       <c r="R3" s="5">
         <v>20</v>
@@ -6983,16 +6983,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2850307665899287</v>
+        <v>0.3226784474596798</v>
       </c>
       <c r="O4" s="5">
         <v>13</v>
       </c>
       <c r="P4" s="4">
-        <v>0.366621543079703</v>
+        <v>0.3780980316141175</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1676928517708513</v>
+        <v>0.1609476750163813</v>
       </c>
       <c r="R4" s="5">
         <v>13</v>
@@ -7042,16 +7042,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.01488648179942482</v>
+        <v>0.1421757822985228</v>
       </c>
       <c r="O5" s="5">
         <v>17</v>
       </c>
       <c r="P5" s="4">
-        <v>0.42923449248569</v>
+        <v>0.4148417507000225</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3876587058611982</v>
+        <v>0.3649631144368287</v>
       </c>
       <c r="R5" s="5">
         <v>17</v>
@@ -7224,16 +7224,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.05229223347108898</v>
+        <v>0.2270222431249067</v>
       </c>
       <c r="O3" s="5">
         <v>23</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3776185081397937</v>
+        <v>0.3297902064251052</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.349941793649776</v>
+        <v>0.2882780608569187</v>
       </c>
       <c r="R3" s="5">
         <v>23</v>
@@ -7281,16 +7281,16 @@
         <v>17</v>
       </c>
       <c r="N4" s="4">
-        <v>3.439347609854036</v>
+        <v>3.240378705781154</v>
       </c>
       <c r="O4" s="5">
         <v>17</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6208901458356597</v>
+        <v>0.5757316281586105</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5366978596479697</v>
+        <v>0.5027440509782851</v>
       </c>
       <c r="R4" s="5">
         <v>17</v>
@@ -7340,22 +7340,22 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.262058003727234</v>
+        <v>0.3214335310509568</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5026612968647636</v>
+        <v>0.4904416488895764</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3575742980315636</v>
+        <v>0.2537749229960894</v>
       </c>
       <c r="R5" s="5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7522,16 +7522,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3622108534729467</v>
+        <v>-0.3469419841196668</v>
       </c>
       <c r="O3" s="5">
         <v>23</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1753295810090787</v>
+        <v>0.1729152090603918</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1858595972170483</v>
+        <v>0.1851218988428736</v>
       </c>
       <c r="R3" s="5">
         <v>23</v>
@@ -7581,16 +7581,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.31724027661393</v>
+        <v>-0.3330851752459694</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1155648971593931</v>
+        <v>0.1137705166157489</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1193822845728747</v>
+        <v>0.1181082496636151</v>
       </c>
       <c r="R4" s="5">
         <v>20</v>
@@ -7640,16 +7640,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2705760760106868</v>
+        <v>-0.2121485089006683</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1642918464338582</v>
+        <v>0.1486741677208972</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1710122128016652</v>
+        <v>0.1623951508110075</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -7822,16 +7822,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1944142705681315</v>
+        <v>-0.1803030250299003</v>
       </c>
       <c r="O3" s="5">
         <v>18</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2966415665985774</v>
+        <v>0.2970421391346353</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2807180677073878</v>
+        <v>0.2796687318229311</v>
       </c>
       <c r="R3" s="5">
         <v>18</v>
@@ -7881,16 +7881,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.0158186446701115</v>
+        <v>-0.07438339785591097</v>
       </c>
       <c r="O4" s="5">
         <v>18</v>
       </c>
       <c r="P4" s="4">
-        <v>0.232841536041673</v>
+        <v>0.219837504311895</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2125638412654584</v>
+        <v>0.2067946294748456</v>
       </c>
       <c r="R4" s="5">
         <v>18</v>
@@ -7940,16 +7940,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.06380739960330217</v>
+        <v>0.1591074029552715</v>
       </c>
       <c r="O5" s="5">
         <v>16</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3967363296364173</v>
+        <v>0.4213272369951889</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4189625610742187</v>
+        <v>0.3677864823437496</v>
       </c>
       <c r="R5" s="5">
         <v>16</v>
@@ -8122,16 +8122,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3055027508417766</v>
+        <v>-0.2070271472449576</v>
       </c>
       <c r="O3" s="5">
         <v>25</v>
       </c>
       <c r="P3" s="4">
-        <v>0.19454451114002</v>
+        <v>0.1691802927974755</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1981830605479936</v>
+        <v>0.1757432976156201</v>
       </c>
       <c r="R3" s="5">
         <v>25</v>
@@ -8181,16 +8181,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1416396956646238</v>
+        <v>-0.1312756335998984</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1243892562109465</v>
+        <v>0.1248047714272961</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1183683590635831</v>
+        <v>0.1174022261793409</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -8240,16 +8240,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2497083249113999</v>
+        <v>-0.126390470261299</v>
       </c>
       <c r="O5" s="5">
         <v>23</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2138738544472435</v>
+        <v>0.2119535294260795</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2135093507221772</v>
+        <v>0.195253610961283</v>
       </c>
       <c r="R5" s="5">
         <v>23</v>
